--- a/public/exports-from-60/29189773.xlsx
+++ b/public/exports-from-60/29189773.xlsx
@@ -11014,12 +11014,12 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311086998</t>
+          <t xml:space="preserve">311086994</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087002</t>
+          <t xml:space="preserve">311086999</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Kolding</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -11539,12 +11539,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087012</t>
+          <t xml:space="preserve">311087008</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087009</t>
+          <t xml:space="preserve">311086987</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Kolding</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -25339,12 +25339,12 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884431</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -25489,12 +25489,12 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884430</t>
+          <t xml:space="preserve">311884429</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900367</t>
+          <t xml:space="preserve">311900366</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
